--- a/assets/constructions/examples/ctd_mc4.xlsx
+++ b/assets/constructions/examples/ctd_mc4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,11 +624,36 @@
           <t>cpdf</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5420-d15</t>
+          <t>7420-d8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -638,7 +663,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5420-ILLICO</t>
+          <t>7420-ILLICO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,7 +673,7 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -659,7 +684,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
@@ -669,7 +694,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>MKG_H:2</t>
+          <t>MKG_H:1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -695,7 +720,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>DIN 1835/1_DIN 844K</t>
+          <t>DIN 1835/1 / DIN 844 K</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -705,15 +730,15 @@
         <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
@@ -745,11 +770,22 @@
       <c r="AM2" t="b">
         <v>0</v>
       </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5420-d12</t>
+          <t>5420-d10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -769,7 +805,7 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -780,7 +816,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -816,7 +852,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>DIN 1835/1_DIN 844K</t>
+          <t>DIN 1835/1 / DIN 844 K</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -830,11 +866,11 @@
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
@@ -866,11 +902,22 @@
       <c r="AM3" t="b">
         <v>0</v>
       </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5420-d36</t>
+          <t>7422C-d32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -880,28 +927,28 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5420-ILLICO</t>
+          <t>7422C-ILLICO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMK</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>k10</t>
+          <t>k12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -932,12 +979,12 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>Tin</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>DIN 1835/1_DIN 844K</t>
+          <t>DIN 228/1 / DIN 845 K</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -951,18 +998,18 @@
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
         <v>30</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -987,11 +1034,22 @@
       <c r="AM4" t="b">
         <v>0</v>
       </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7424-d15</t>
+          <t>7420-d10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1001,7 +1059,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7424-ILLICO</t>
+          <t>7420-ILLICO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1011,7 +1069,7 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -1022,7 +1080,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -1032,7 +1090,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MKG_H:2</t>
+          <t>MKG_H:1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1058,7 +1116,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>DIN 1835/1_DIN 844K</t>
+          <t>DIN 1835/1 / DIN 844 K</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -1068,15 +1126,15 @@
         <v>4</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
@@ -1108,11 +1166,22 @@
       <c r="AM5" t="b">
         <v>0</v>
       </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5420-d18</t>
+          <t>5416-d45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1122,7 +1191,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5420-ILLICO</t>
+          <t>5416-ILLICO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1132,7 +1201,7 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -1153,7 +1222,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>MKG_H:2</t>
+          <t>MKG_H:4</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1179,17 +1248,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>DIN 1835/1_DIN 844K</t>
+          <t>DIN 1835/1 / DIN 844 K</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="n">
         <v>4</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
@@ -1197,7 +1266,7 @@
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
@@ -1229,6 +1298,17 @@
       <c r="AM6" t="b">
         <v>0</v>
       </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
